--- a/data/clean/cropburn/codebook.xlsx
+++ b/data/clean/cropburn/codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haya1/Documents/rsv_cropburning/data/clean/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haya1/MIT Dropbox/Haya Alsharif/analysis_image_project/rsv_replication/data/clean/cropburn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F65334-67DC-4A41-B725-6071A919BFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCFC7E6-BF80-3148-9934-420FB21AEC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="780" windowWidth="25600" windowHeight="14360" xr2:uid="{EAA0BB47-4334-024B-9D8E-1155054D2651}"/>
+    <workbookView xWindow="13140" yWindow="780" windowWidth="25600" windowHeight="14360" xr2:uid="{EAA0BB47-4334-024B-9D8E-1155054D2651}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Variable Name</t>
   </si>
@@ -31,15 +31,6 @@
     <t>village_id</t>
   </si>
   <si>
-    <t>treatment</t>
-  </si>
-  <si>
-    <t>pesonly</t>
-  </si>
-  <si>
-    <t>pesuct</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -58,78 +49,15 @@
     <t>district</t>
   </si>
   <si>
-    <t>tv_name</t>
-  </si>
-  <si>
     <t>Unique identifier for each village, as defined in Kelsey Jack et al. (2022).</t>
   </si>
   <si>
-    <t>Binary indicator for villages assigned to PES-only treatment arms: 1 = Village is in either PES 800/acre or PES 1600/acre treatment arms; 0 = Otherwise.</t>
-  </si>
-  <si>
-    <t>Binary indicator for villages assigned to PES treatment with upfront payments: 1 = Village is in either PES 800/acre with 25% upfront payment or PES 800/acre with 50% upfront payment; 0 = Otherwise</t>
-  </si>
-  <si>
-    <t>Binary indicator for villages assigned to any PES treatment arm: 1 = Village is in any PES treatment arm; 0 = Village is in the Control group.</t>
-  </si>
-  <si>
     <t>Name of the district where the village is located, either Bathinda or Faridkot. Used for stratifying initial treatment assignment.</t>
   </si>
   <si>
-    <t>Binary indicator for baseline survey completion: 1 = Baseline survey was completed in the village; 0 = Otherwise. Used for stratifying initial treatment assignment.</t>
-  </si>
-  <si>
-    <t>Binary indicator for listing survey completion: 1 = Listing survey was not completed in the village; 0 = Otherwise. Used for stratifying initial treatment assignment.</t>
-  </si>
-  <si>
     <t>Indicator for villages randomly added to treatment arms to supplement sample size. These 15 villages had listing surveys covering between 6 to 17 households. Used for stratifying initial treatment assignment.</t>
   </si>
   <si>
-    <t>Binary indicator for whether a village has an above-median number of eligible households (based on phone listing survey): 1 = Above-median number of eligible households; 0 = Otherwise. Used for stratifying initial treatment assignment.</t>
-  </si>
-  <si>
-    <t>Name of the village based on Kelsey Jack et al. (2022) naming convention.</t>
-  </si>
-  <si>
-    <t>resp_id</t>
-  </si>
-  <si>
-    <t>unique_plot_id</t>
-  </si>
-  <si>
-    <t>complied</t>
-  </si>
-  <si>
-    <t>is_sc</t>
-  </si>
-  <si>
-    <t>is_mon</t>
-  </si>
-  <si>
-    <t>inv_n_fields</t>
-  </si>
-  <si>
-    <t>Unique identifier for each farmer, as defined in Kelsey Jack et al. (2022).</t>
-  </si>
-  <si>
-    <t>Unique identifier for each field/plot, as defined in Kelsey Jack et al. (2022).</t>
-  </si>
-  <si>
-    <t>The assigned treatment arm for the village. Villages are assigned to one of five groups: (1) PES 800/acre, (2) PES 1600/acre, (3) PES 800/acre with 25% upfront payment, (4) PES 800/acre with 50% upfront payment, and (5) Control.</t>
-  </si>
-  <si>
-    <t>1 = Field was not burned based on a Random Forest model with a threshold to maximize overall accuracy; 0 = Otherwise</t>
-  </si>
-  <si>
-    <t>1 = Field was not burned, based on a Random Forest model with a threshold to balance sensitivity and specificity; 0 = Otherwise</t>
-  </si>
-  <si>
-    <t>Inverse of the number of fields owned by the farmer who owns this field.</t>
-  </si>
-  <si>
-    <t>1 = Field belongs to a compliant farmer (based on monitoring data); 0 = Field belongs to a non-compliant farmer.</t>
-  </si>
-  <si>
     <t>R_prob</t>
   </si>
   <si>
@@ -139,25 +67,10 @@
     <t>R_bal</t>
   </si>
   <si>
-    <t>Y_sc</t>
-  </si>
-  <si>
-    <t>Y_mon</t>
-  </si>
-  <si>
     <t>Y_original</t>
   </si>
   <si>
-    <t>Y_ours</t>
-  </si>
-  <si>
     <t>Y_original_recon</t>
-  </si>
-  <si>
-    <t>is_scmon</t>
-  </si>
-  <si>
-    <t>is_scmon_orignial</t>
   </si>
   <si>
     <t>Predicted probabilities from the Random Forest model, [0,1]</t>
@@ -169,34 +82,47 @@
 NA = Field lacks ground truth data</t>
   </si>
   <si>
-    <t>1 = Field was not burned, according to monitoring data; 
-0 = Field was burned, according to monitoring data; 
-NA = Field lacks monitoring data</t>
-  </si>
-  <si>
-    <t>1 = Field was not burned, according to spot-check data; 
-0 = Field was burned, according to spot-check data; 
-NA = Field lacks spot-check data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Our attempt to reconstruct Y_original using Y_sc and Y_mon. </t>
-  </si>
-  <si>
-    <t>If a field is a spot-check field, then Y_ours = Y_sc;
-If a field is a monitoring-only field, then Y_ours = Y_mon; 
-If a field is neither a spot-check nor a monitoring-only, Y_ours = NA</t>
-  </si>
-  <si>
-    <t>1 = Spot-check field (i.e., Y_sc is not missing); 0 = Otherwise.</t>
-  </si>
-  <si>
-    <t>1 = Monitoring field (i.e., Y_mon is not missing); 0 = Otherwise.</t>
-  </si>
-  <si>
-    <t>1 = Spot-check or monitoring field (i.e., Y_sc or Y_mon is not missing); 0 = Otherwise.</t>
-  </si>
-  <si>
-    <t>1 = Field has ground truth outcome as defined in  Kelsey Jack et al. (2022), (i.e., Y_original is not missing); 0 = Otherwise.</t>
+    <t>pc11_tv_id</t>
+  </si>
+  <si>
+    <t>Our attempt to reconstruct Y_original.</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Unique identifier for each village, as defined in SHRUG 2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary indicator for whether a village has an above-median number of eligible households (based on phone listing survey). Used for stratifying initial treatment assignment.
+1 = Above-median number of eligible households; 
+0 = Otherwise. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary indicator for listing survey completion. Used for stratifying initial treatment assignment.
+1 = Listing survey was not completed in the village; 
+0 = Otherwise. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary indicator for baseline survey completion. Used for stratifying initial treatment assignment.
+1 = Baseline survey was completed in the village; 
+0 = Otherwise. </t>
+  </si>
+  <si>
+    <t>Binary indicator for villages assigned to any PES treatment arm: 
+1 = Village is in any PES treatment arm; 
+0 = Village is in the Control group.</t>
+  </si>
+  <si>
+    <t>1 = Field was not burned, based on a Random Forest model with a threshold to balance sensitivity and specificity; 
+0 = Otherwise</t>
+  </si>
+  <si>
+    <t>1 = Field was not burned based on a Random Forest model with a threshold to maximize overall accuracy;
+ 0 = Otherwise</t>
+  </si>
+  <si>
+    <t>"o" = Observational field defined as fields that received a random spot-check; "e" = Expermental fields include all other fields.</t>
   </si>
 </sst>
 </file>
@@ -760,8 +686,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63B1AA0E-B2EE-404A-8B39-79BF53AAA5E8}" name="Table1" displayName="Table1" ref="A1:B28" totalsRowShown="0">
-  <autoFilter ref="A1:B28" xr:uid="{63B1AA0E-B2EE-404A-8B39-79BF53AAA5E8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63B1AA0E-B2EE-404A-8B39-79BF53AAA5E8}" name="Table1" displayName="Table1" ref="A1:B15" totalsRowShown="0">
+  <autoFilter ref="A1:B15" xr:uid="{63B1AA0E-B2EE-404A-8B39-79BF53AAA5E8}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{48E5528A-3714-1441-B998-0BDE8CC60CA0}" name="Variable Name"/>
     <tableColumn id="2" xr3:uid="{DCA21F7E-3553-2D4A-9155-DCE47B238240}" name="Variable Description" dataDxfId="0"/>
@@ -1087,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F672021C-381F-B64C-A40C-DAD57732CE04}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
@@ -1108,68 +1034,68 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>17</v>
@@ -1177,162 +1103,58 @@
     </row>
     <row r="11" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="68" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="51" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B32" s="4"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B36" s="4"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
